--- a/materials/introduction.xlsx
+++ b/materials/introduction.xlsx
@@ -1,110 +1,110 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Lehre\Introduction to Programming\Presentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E550A0B6-8AFD-4B49-9C1F-2F5618A098A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="75" windowWidth="12000" windowHeight="7245"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="22365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Anfang" sheetId="4" r:id="rId1"/>
-    <sheet name="Maske" sheetId="7" r:id="rId2"/>
-    <sheet name="mit Graphik" sheetId="1" r:id="rId3"/>
-    <sheet name="Einfach" sheetId="6" r:id="rId4"/>
-    <sheet name="Wenn" sheetId="5" r:id="rId5"/>
-    <sheet name="Solver" sheetId="8" r:id="rId6"/>
+    <sheet name="Start" sheetId="4" r:id="rId1"/>
+    <sheet name="Cost_Revenue" sheetId="7" r:id="rId2"/>
+    <sheet name="with_plot" sheetId="1" r:id="rId3"/>
+    <sheet name="simple" sheetId="6" r:id="rId4"/>
+    <sheet name="conditional_cost" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="25">
   <si>
-    <t>Erlöse</t>
-  </si>
-  <si>
-    <t>Kosten- und Erlösrechnung</t>
-  </si>
-  <si>
-    <t>Fixkosten (Jahr) =</t>
-  </si>
-  <si>
-    <t>var. Kosten (Stück) =</t>
-  </si>
-  <si>
-    <t>Preis (Stück) =</t>
-  </si>
-  <si>
-    <t>Monat</t>
-  </si>
-  <si>
-    <t>Januar</t>
-  </si>
-  <si>
-    <t>Februar</t>
-  </si>
-  <si>
-    <t>März</t>
-  </si>
-  <si>
     <t>April</t>
   </si>
   <si>
-    <t>Mai</t>
-  </si>
-  <si>
-    <t>Juni</t>
-  </si>
-  <si>
-    <t>Juli</t>
-  </si>
-  <si>
     <t>August</t>
   </si>
   <si>
     <t>September</t>
   </si>
   <si>
-    <t>Oktober</t>
-  </si>
-  <si>
     <t>November</t>
   </si>
   <si>
-    <t>Dezember</t>
-  </si>
-  <si>
-    <t>Gesamt</t>
-  </si>
-  <si>
-    <t>Erlös (Stück) =</t>
-  </si>
-  <si>
-    <t>Gewinn (Jahr) =</t>
-  </si>
-  <si>
-    <t>Fixkosten (Jahr):</t>
-  </si>
-  <si>
-    <t>Gesamt &lt; 130000 =</t>
-  </si>
-  <si>
-    <t>Gesamt &gt;= 130000 =</t>
-  </si>
-  <si>
-    <t>Produktion</t>
+    <t>Cost and revenue calculation</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Price (per unit) =</t>
+  </si>
+  <si>
+    <t>var. Cost (per unit) =</t>
+  </si>
+  <si>
+    <t>Revenue (per unti) =</t>
+  </si>
+  <si>
+    <t>Fixed cost (per year) =</t>
+  </si>
+  <si>
+    <t>Profit (per year) =</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Fixed cost (per year):</t>
+  </si>
+  <si>
+    <t>Production &lt; 130000 =</t>
+  </si>
+  <si>
+    <t>Production &gt;= 130000 =</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -168,7 +168,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -180,7 +179,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -457,9 +456,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <headerFooter alignWithMargins="0"/>
@@ -467,34 +466,34 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="A1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -502,13 +501,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>10000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -516,19 +515,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>12000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -536,13 +535,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>250000</v>
@@ -550,7 +549,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -558,34 +557,34 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>11000</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
         <v>12000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>15000</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -593,7 +592,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -601,7 +600,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -609,7 +608,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1">
         <v>8000</v>
@@ -628,9 +627,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
@@ -638,13 +637,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="A1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
       <c r="F1" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -652,13 +651,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -666,7 +665,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>10000</v>
@@ -676,7 +675,7 @@
         <v>20000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -684,7 +683,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>12000</v>
@@ -693,8 +692,8 @@
         <f t="shared" ref="C5:C15" si="0">B5*$E$5</f>
         <v>24000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E5" s="3">
         <f>E3-E4</f>
@@ -703,7 +702,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -715,7 +714,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
@@ -724,8 +723,8 @@
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
+      <c r="D7" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="E7">
         <v>250000</v>
@@ -733,7 +732,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -745,7 +744,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>11000</v>
@@ -755,14 +754,14 @@
         <v>22000</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
         <v>12000</v>
       </c>
       <c r="C10">
@@ -771,10 +770,10 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>15000</v>
       </c>
       <c r="C11">
@@ -784,7 +783,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -796,7 +795,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -808,7 +807,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -820,7 +819,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1">
         <v>8000</v>
@@ -844,35 +843,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="A1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -880,7 +879,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>10000</v>
@@ -890,7 +889,7 @@
         <v>20000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -898,7 +897,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>12000</v>
@@ -907,8 +906,8 @@
         <f t="shared" ref="C5:C15" si="0">B5*$E$5</f>
         <v>24000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E5" s="3">
         <f>E3-E4</f>
@@ -917,7 +916,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -929,7 +928,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
@@ -939,7 +938,7 @@
         <v>18000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>250000</v>
@@ -947,7 +946,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -959,7 +958,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>11000</v>
@@ -969,14 +968,14 @@
         <v>22000</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
         <v>12000</v>
       </c>
       <c r="C10">
@@ -985,10 +984,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>15000</v>
       </c>
       <c r="C11">
@@ -998,7 +997,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -1010,7 +1009,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -1022,7 +1021,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -1034,7 +1033,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1">
         <v>8000</v>
@@ -1046,7 +1045,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3"/>
     </row>
@@ -1060,9 +1059,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="23.28515625" customWidth="1"/>
@@ -1070,26 +1069,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="A1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -1097,7 +1096,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>10000</v>
@@ -1107,7 +1106,7 @@
         <v>20000</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>18</v>
@@ -1115,7 +1114,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>12000</v>
@@ -1124,8 +1123,8 @@
         <f t="shared" ref="C5:C15" si="0">B5*$E$5</f>
         <v>24000</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="E5" s="3">
         <f>E3-E4</f>
@@ -1134,7 +1133,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>13000</v>
@@ -1146,7 +1145,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>9000</v>
@@ -1155,13 +1154,13 @@
         <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
+      <c r="D7" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>8000</v>
@@ -1171,7 +1170,7 @@
         <v>16000</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>200000</v>
@@ -1179,7 +1178,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>11000</v>
@@ -1189,42 +1188,42 @@
         <v>22000</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>250000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>12000</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>15000</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" s="6">
-        <v>12000</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
-        <v>15000</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12">
         <v>13000</v>
@@ -1236,7 +1235,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>11000</v>
@@ -1248,7 +1247,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>9000</v>
@@ -1260,7 +1259,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1">
         <v>8000</v>
@@ -1272,7 +1271,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <f>SUM(B4:B15)</f>
@@ -1290,14 +1289,4 @@
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/materials/introduction.xlsx
+++ b/materials/introduction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E550A0B6-8AFD-4B49-9C1F-2F5618A098A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476F2C6A-EE33-472A-BEA7-5A6D40DE1B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="22365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="4" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="with_plot" sheetId="1" r:id="rId3"/>
     <sheet name="simple" sheetId="6" r:id="rId4"/>
     <sheet name="conditional_cost" sheetId="5" r:id="rId5"/>
+    <sheet name="Bike_sales" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
   <si>
     <t>April</t>
   </si>
@@ -99,13 +100,40 @@
   </si>
   <si>
     <t>Production &gt;= 130000 =</t>
+  </si>
+  <si>
+    <t>Bike</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>City-Trip</t>
+  </si>
+  <si>
+    <t>TourenCross</t>
+  </si>
+  <si>
+    <t>MTB-Downhill</t>
+  </si>
+  <si>
+    <t>MTB-SingleTrail</t>
+  </si>
+  <si>
+    <t>MTB-Monster</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -116,6 +144,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -125,7 +161,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -151,11 +187,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -177,6 +228,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1289,4 +1344,101 @@
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A600789-C080-4141-B61C-543C0E3F31D0}">
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="B2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="10">
+        <v>3</v>
+      </c>
+      <c r="D3" s="10">
+        <v>7797</v>
+      </c>
+      <c r="E3" s="10">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="10">
+        <v>5</v>
+      </c>
+      <c r="D4" s="10">
+        <v>18995</v>
+      </c>
+      <c r="E4" s="10">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <v>5799</v>
+      </c>
+      <c r="E5" s="10">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="10">
+        <v>4</v>
+      </c>
+      <c r="D6" s="10">
+        <v>29996</v>
+      </c>
+      <c r="E6" s="10">
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="10">
+        <v>9</v>
+      </c>
+      <c r="D7" s="10">
+        <v>89910</v>
+      </c>
+      <c r="E7" s="10">
+        <v>75600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/materials/introduction.xlsx
+++ b/materials/introduction.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476F2C6A-EE33-472A-BEA7-5A6D40DE1B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60824C8A-2FB1-49B7-B68B-9F79753FEF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="4" r:id="rId1"/>
     <sheet name="Cost_Revenue" sheetId="7" r:id="rId2"/>
-    <sheet name="with_plot" sheetId="1" r:id="rId3"/>
-    <sheet name="simple" sheetId="6" r:id="rId4"/>
-    <sheet name="conditional_cost" sheetId="5" r:id="rId5"/>
-    <sheet name="Bike_sales" sheetId="8" r:id="rId6"/>
+    <sheet name="Cost_Revenue_Painter" sheetId="9" r:id="rId3"/>
+    <sheet name="with_plot" sheetId="1" r:id="rId4"/>
+    <sheet name="simple" sheetId="6" r:id="rId5"/>
+    <sheet name="conditional_cost" sheetId="5" r:id="rId6"/>
+    <sheet name="Bike_sales" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="39">
   <si>
     <t>April</t>
   </si>
@@ -127,13 +139,28 @@
   </si>
   <si>
     <t>MTB-Monster</t>
+  </si>
+  <si>
+    <t>Colors</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Patterns</t>
+  </si>
+  <si>
+    <t>Size (m²)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -151,6 +178,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -206,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -222,16 +254,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,13 +568,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -682,6 +721,123 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B81E67B7-CC88-4D25-9788-DCF812CA07CE}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C3" s="12">
+        <v>2</v>
+      </c>
+      <c r="D3" s="12">
+        <v>4</v>
+      </c>
+      <c r="E3" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <f>$B4*C$3</f>
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:E7" si="0">$B4*D$3</f>
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:E7" si="1">$B5*C$3</f>
+        <v>40</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="13"/>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="13"/>
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A4:A7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -692,13 +848,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
       <c r="F1" s="4"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -897,7 +1053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -907,13 +1063,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1113,7 +1269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1124,13 +1280,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1346,7 +1502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A600789-C080-4141-B61C-543C0E3F31D0}">
   <dimension ref="B2:E7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1355,86 +1511,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="8">
         <v>3</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="8">
         <v>7797</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="8">
         <v>4410</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>5</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="8">
         <v>18995</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>12500</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>1</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>5799</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>4800</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="8">
         <v>4</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>29996</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="8">
         <v>19200</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="8">
         <v>9</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="8">
         <v>89910</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="8">
         <v>75600</v>
       </c>
     </row>
